--- a/artfynd/A 31695-2024 artfynd.xlsx
+++ b/artfynd/A 31695-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>118491002</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31695-2024 artfynd.xlsx
+++ b/artfynd/A 31695-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>87178142</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528084.3644834441</v>
+        <v>528084</v>
       </c>
       <c r="R2" t="n">
-        <v>6577624.162811643</v>
+        <v>6577624</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118491002</v>
+        <v>102636168</v>
       </c>
       <c r="B3" t="n">
-        <v>97833</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,17 +801,21 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vallaholm, N Kärsta, Lillkyrka, Nrk</t>
+          <t>S Vallholma, Kärsta, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528109</v>
+        <v>528011</v>
       </c>
       <c r="R3" t="n">
-        <v>6577604</v>
+        <v>6577716</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,6 +856,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,6 +872,301 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102639587</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogsväg N Prästtorp, Kärsta, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>528083</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6577654</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lillkyrka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111266948</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vallaholm, Norra Kärsta, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528027</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6577704</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lillkyrka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118491002</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vallaholm, N Kärsta, Lillkyrka, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>528109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6577604</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lillkyrka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31695-2024 artfynd.xlsx
+++ b/artfynd/A 31695-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87178142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102636168</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102639587</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111266948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,8 +1192,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118491002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>